--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="周模板" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>年份</t>
+  </si>
+  <si>
+    <t>数据类型（市场数据，供应链数据，经营数据，财务数据）</t>
   </si>
   <si>
     <t>指标分类</t>
@@ -1002,14 +1005,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1028,10 +1031,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="周模板" sheetId="1" r:id="rId1"/>
@@ -13,31 +13,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+例如：2021年</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+例如：12月1日-12月7日</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>年份</t>
+    <t>*年份</t>
   </si>
   <si>
-    <t>数据类型（市场数据，供应链数据，经营数据，财务数据）</t>
+    <t>*数据类型</t>
   </si>
   <si>
-    <t>指标分类</t>
+    <t>*指标分类</t>
   </si>
   <si>
-    <t>指标名称</t>
+    <t>*指标名称</t>
   </si>
   <si>
-    <t>目标值</t>
-  </si>
-  <si>
-    <t>12月1日-12月7日</t>
-  </si>
-  <si>
-    <t>12月8日-12月15日</t>
-  </si>
-  <si>
-    <t>2021年</t>
+    <t>*目标值</t>
   </si>
 </sst>
 </file>
@@ -50,7 +95,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +246,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1005,14 +1061,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1028,21 +1084,17 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
+      <c r="F1"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"市场数据,供应链数据,经营数据,财务数据"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
+++ b/erp-server/erp-server-bi/src/main/resources/excel/biDataSourceCustomWeek.xlsx
@@ -41,7 +41,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -68,15 +68,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>*年份</t>
   </si>
   <si>
-    <t>*数据类型</t>
-  </si>
-  <si>
-    <t>*指标分类</t>
+    <t>指标分类</t>
   </si>
   <si>
     <t>*指标名称</t>
@@ -1061,14 +1058,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1081,17 +1078,9 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1"/>
+      <c r="E1"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>"市场数据,供应链数据,经营数据,财务数据"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
